--- a/correos/correos_FINAL.xlsx
+++ b/correos/correos_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educacionpublica-my.sharepoint.com/personal/alonso_arrano_dep_cl/Documents/2024/SAE - Anotate en la lista/reporteria_ael/correos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="341" documentId="11_AD4D2F04E46CFB4ACB3E20CA8550FF6C693EDF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E6ED773-D2D1-4669-8DAB-3429CC09303A}"/>
+  <xr:revisionPtr revIDLastSave="350" documentId="11_AD4D2F04E46CFB4ACB3E20CA8550FF6C693EDF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{059AF893-8D40-44C5-AEB3-039CA605E834}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="259">
   <si>
     <t>Tipo_SLEP</t>
   </si>
@@ -69,9 +69,6 @@
     <t>copia</t>
   </si>
   <si>
-    <t>archivo</t>
-  </si>
-  <si>
     <t>Antiguo</t>
   </si>
   <si>
@@ -93,9 +90,6 @@
     <t>jocelyn.almonacid@slepllanquihue.cl</t>
   </si>
   <si>
-    <t>reporte_llanquihue.html</t>
-  </si>
-  <si>
     <t>Chiloé</t>
   </si>
   <si>
@@ -114,9 +108,6 @@
     <t>Altircio.sarmiento@slepchiloe.gob.cl</t>
   </si>
   <si>
-    <t>reporte_Chiloé.html</t>
-  </si>
-  <si>
     <t>Valdivia</t>
   </si>
   <si>
@@ -129,9 +120,6 @@
     <t>jasmin.sanmartin@slepvaldivia.gob.cl</t>
   </si>
   <si>
-    <t>reporte_valdivia.html</t>
-  </si>
-  <si>
     <t>Santa Rosa</t>
   </si>
   <si>
@@ -147,9 +135,6 @@
     <t>josefina.abarzua@slepsantarosa.gob.cl</t>
   </si>
   <si>
-    <t>reporte_santa_rosa.html</t>
-  </si>
-  <si>
     <t>Santa Corina</t>
   </si>
   <si>
@@ -162,9 +147,6 @@
     <t>juan.duran@slepsantacorina.gob.cl</t>
   </si>
   <si>
-    <t>reporte_santa_corina.html</t>
-  </si>
-  <si>
     <t>Maule Costa</t>
   </si>
   <si>
@@ -177,9 +159,6 @@
     <t>yolanda.urrutia@slepmaulecosta.gob.cl</t>
   </si>
   <si>
-    <t>reporte_maule_costa.html</t>
-  </si>
-  <si>
     <t>Los Libertadores</t>
   </si>
   <si>
@@ -192,9 +171,6 @@
     <t>manuel.coloma@sleploslibertadores.gob.cl</t>
   </si>
   <si>
-    <t>reporte_los_libertadores.html</t>
-  </si>
-  <si>
     <t>Licancabur</t>
   </si>
   <si>
@@ -207,9 +183,6 @@
     <t>david.cruz@sleplicancabur.cl</t>
   </si>
   <si>
-    <t>reporte_licancabur.html</t>
-  </si>
-  <si>
     <t>Andalién Costa</t>
   </si>
   <si>
@@ -225,9 +198,6 @@
     <t>marcela.valencia@slepandaliencosta.gob.cl</t>
   </si>
   <si>
-    <t>reporte_andalién_costa.html</t>
-  </si>
-  <si>
     <t>Del Pino</t>
   </si>
   <si>
@@ -240,9 +210,6 @@
     <t>rodrigo.yanez@edudelpino.gob.cl</t>
   </si>
   <si>
-    <t>reporte_del_pino.html</t>
-  </si>
-  <si>
     <t>Punilla Cordillera</t>
   </si>
   <si>
@@ -258,9 +225,6 @@
     <t>karla.sepulveda@sleppunillacordillera.cl</t>
   </si>
   <si>
-    <t>reporte_punilla_cordillera.html</t>
-  </si>
-  <si>
     <t>Magallanes</t>
   </si>
   <si>
@@ -273,9 +237,6 @@
     <t>carolina.figueroa@slepmagallanes.cl</t>
   </si>
   <si>
-    <t>reporte_magallanes.html</t>
-  </si>
-  <si>
     <t>Aysen</t>
   </si>
   <si>
@@ -291,9 +252,6 @@
     <t>freddy.moraga@slepaysen.cl</t>
   </si>
   <si>
-    <t>reporte_aysén.html</t>
-  </si>
-  <si>
     <t xml:space="preserve">Iquique </t>
   </si>
   <si>
@@ -306,9 +264,6 @@
     <t>mario.reyes@slepiquique.cl</t>
   </si>
   <si>
-    <t>reporte_iquique.html</t>
-  </si>
-  <si>
     <t>Costa Araucanía</t>
   </si>
   <si>
@@ -321,9 +276,6 @@
     <t>sandra.padilla@slepca.cl</t>
   </si>
   <si>
-    <t>reporte_costa_araucanía.html</t>
-  </si>
-  <si>
     <t xml:space="preserve">Atacama </t>
   </si>
   <si>
@@ -336,9 +288,6 @@
     <t>marcelo.quiroga@slepatacama.cl</t>
   </si>
   <si>
-    <t>reporte_atacama.html</t>
-  </si>
-  <si>
     <t>Huasco</t>
   </si>
   <si>
@@ -351,9 +300,6 @@
     <t>maryorie.alquinta@slephuasco.cl</t>
   </si>
   <si>
-    <t>reporte_huasco.html</t>
-  </si>
-  <si>
     <t>Puerto Cordillera</t>
   </si>
   <si>
@@ -366,9 +312,6 @@
     <t>margarita.campillo@slepuertocordillera.cl</t>
   </si>
   <si>
-    <t>reporte_puerto_cordillera.html</t>
-  </si>
-  <si>
     <t>Valparaíso</t>
   </si>
   <si>
@@ -381,9 +324,6 @@
     <t>angeline.castillo@slepvalparaiso.cl</t>
   </si>
   <si>
-    <t>reporte_valparaíso.html</t>
-  </si>
-  <si>
     <t>Barrancas</t>
   </si>
   <si>
@@ -396,9 +336,6 @@
     <t>daniela.chamorro@slepb.cl</t>
   </si>
   <si>
-    <t>reporte_barrancas.html</t>
-  </si>
-  <si>
     <t>Gabriela Mistral</t>
   </si>
   <si>
@@ -411,9 +348,6 @@
     <t>marta.hinojosa@slepgm.cl</t>
   </si>
   <si>
-    <t>reporte_gabriela_mistral.html</t>
-  </si>
-  <si>
     <t>Colchagua</t>
   </si>
   <si>
@@ -426,9 +360,6 @@
     <t>oscar.ubilla@slepcolchagua.cl</t>
   </si>
   <si>
-    <t>reporte_colchagua.html</t>
-  </si>
-  <si>
     <t>Andalién Sur</t>
   </si>
   <si>
@@ -441,9 +372,6 @@
     <t>elena.saez@andaliensur.cl</t>
   </si>
   <si>
-    <t>reporte_andalién_sur.html</t>
-  </si>
-  <si>
     <t>Chinchorro</t>
   </si>
   <si>
@@ -459,9 +387,6 @@
     <t>shirley.villegas@epchinchorro.cl</t>
   </si>
   <si>
-    <t>reporte_chinchorro.html</t>
-  </si>
-  <si>
     <t>Costa Central</t>
   </si>
   <si>
@@ -474,9 +399,6 @@
     <t>tomas.gonzalez@slepcostacentral.gob.cl</t>
   </si>
   <si>
-    <t>reporte_costa_central.html</t>
-  </si>
-  <si>
     <t>Elqui</t>
   </si>
   <si>
@@ -492,9 +414,6 @@
     <t>marco.vega@slepelqui.gob.cl</t>
   </si>
   <si>
-    <t>reporte_elqui.html</t>
-  </si>
-  <si>
     <t>Nuevo</t>
   </si>
   <si>
@@ -516,9 +435,6 @@
     <t>mauricio.urrutia@sleppetorca.gob.cl</t>
   </si>
   <si>
-    <t>reporte_petorca.html</t>
-  </si>
-  <si>
     <t>Los Andes</t>
   </si>
   <si>
@@ -537,9 +453,6 @@
     <t>felipe.martinez@sleplosandes.gob.cl</t>
   </si>
   <si>
-    <t>reporte_los_andes.html</t>
-  </si>
-  <si>
     <t>Aconcagua</t>
   </si>
   <si>
@@ -558,9 +471,6 @@
     <t>yasna.flos@slepaconcagua.gob.cl</t>
   </si>
   <si>
-    <t>reporte_aconcagua.html</t>
-  </si>
-  <si>
     <t>Puelche</t>
   </si>
   <si>
@@ -579,9 +489,6 @@
     <t>rossemarie.sanchez@sleppuelche.gob.cl</t>
   </si>
   <si>
-    <t>reporte_puelche.html</t>
-  </si>
-  <si>
     <t>Los Álamos</t>
   </si>
   <si>
@@ -600,9 +507,6 @@
     <t>ximena.valenzuela@sleplosalamos.gob.cl</t>
   </si>
   <si>
-    <t>reporte_los_álamos.html</t>
-  </si>
-  <si>
     <t>Marga Marga</t>
   </si>
   <si>
@@ -621,9 +525,6 @@
     <t>jorge.manchini@slepmargamarga.gob.cl</t>
   </si>
   <si>
-    <t>reporte_marga_marga.html</t>
-  </si>
-  <si>
     <t>Los Parques</t>
   </si>
   <si>
@@ -642,9 +543,6 @@
     <t>flavia.fiabane@sleplosparques.gob.cl</t>
   </si>
   <si>
-    <t>reporte_los_parques.html</t>
-  </si>
-  <si>
     <t>Tamarugal</t>
   </si>
   <si>
@@ -663,9 +561,6 @@
     <t>samuel.diaz@sleptamarugal.gob.cl</t>
   </si>
   <si>
-    <t>reporte_tamarugal.html</t>
-  </si>
-  <si>
     <t>Santiago Centro</t>
   </si>
   <si>
@@ -684,9 +579,6 @@
     <t>juan.saez@slepsantiagocentro.gob.cl</t>
   </si>
   <si>
-    <t>reporte_santiago_centro.html</t>
-  </si>
-  <si>
     <t>Valle Diguillín</t>
   </si>
   <si>
@@ -705,14 +597,233 @@
     <t>sergio.hernandez@slepvallediguillin.gob.cl</t>
   </si>
   <si>
-    <t>reporte_Valle_Diguillín.html</t>
+    <t>archivo1</t>
+  </si>
+  <si>
+    <t>reporte_llanquihue.pdf</t>
+  </si>
+  <si>
+    <t>reporte_Chiloé.pdf</t>
+  </si>
+  <si>
+    <t>reporte_valdivia.pdf</t>
+  </si>
+  <si>
+    <t>reporte_santa_rosa.pdf</t>
+  </si>
+  <si>
+    <t>reporte_santa_corina.pdf</t>
+  </si>
+  <si>
+    <t>reporte_maule_costa.pdf</t>
+  </si>
+  <si>
+    <t>reporte_los_libertadores.pdf</t>
+  </si>
+  <si>
+    <t>reporte_licancabur.pdf</t>
+  </si>
+  <si>
+    <t>reporte_andalién_costa.pdf</t>
+  </si>
+  <si>
+    <t>reporte_del_pino.pdf</t>
+  </si>
+  <si>
+    <t>reporte_punilla_cordillera.pdf</t>
+  </si>
+  <si>
+    <t>reporte_magallanes.pdf</t>
+  </si>
+  <si>
+    <t>reporte_aysén.pdf</t>
+  </si>
+  <si>
+    <t>reporte_iquique.pdf</t>
+  </si>
+  <si>
+    <t>reporte_costa_araucanía.pdf</t>
+  </si>
+  <si>
+    <t>reporte_atacama.pdf</t>
+  </si>
+  <si>
+    <t>reporte_huasco.pdf</t>
+  </si>
+  <si>
+    <t>reporte_puerto_cordillera.pdf</t>
+  </si>
+  <si>
+    <t>reporte_valparaíso.pdf</t>
+  </si>
+  <si>
+    <t>reporte_barrancas.pdf</t>
+  </si>
+  <si>
+    <t>reporte_gabriela_mistral.pdf</t>
+  </si>
+  <si>
+    <t>reporte_colchagua.pdf</t>
+  </si>
+  <si>
+    <t>reporte_andalién_sur.pdf</t>
+  </si>
+  <si>
+    <t>reporte_chinchorro.pdf</t>
+  </si>
+  <si>
+    <t>reporte_costa_central.pdf</t>
+  </si>
+  <si>
+    <t>reporte_elqui.pdf</t>
+  </si>
+  <si>
+    <t>reporte_petorca.pdf</t>
+  </si>
+  <si>
+    <t>reporte_los_andes.pdf</t>
+  </si>
+  <si>
+    <t>reporte_aconcagua.pdf</t>
+  </si>
+  <si>
+    <t>reporte_puelche.pdf</t>
+  </si>
+  <si>
+    <t>reporte_los_álamos.pdf</t>
+  </si>
+  <si>
+    <t>reporte_marga_marga.pdf</t>
+  </si>
+  <si>
+    <t>reporte_los_parques.pdf</t>
+  </si>
+  <si>
+    <t>reporte_tamarugal.pdf</t>
+  </si>
+  <si>
+    <t>reporte_santiago_centro.pdf</t>
+  </si>
+  <si>
+    <t>reporte_Valle_Diguillín.pdf</t>
+  </si>
+  <si>
+    <t>archivo2</t>
+  </si>
+  <si>
+    <t>AEL_llanquihue.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_Chiloé.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_valdivia.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_santa_rosa.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_santa_corina.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_maule_costa.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_los_libertadores.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_licancabur.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_andalién_costa.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_del_pino.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_punilla_cordillera.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_magallanes.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_aysén.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_iquique.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_costa_araucanía.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_atacama.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_huasco.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_puerto_cordillera.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_valparaíso.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_barrancas.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_gabriela_mistral.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_colchagua.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_andalién_sur.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_chinchorro.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_costa_central.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_elqui.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_petorca.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_los_andes.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_aconcagua.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_puelche.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_los_álamos.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_marga_marga.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_los_parques.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_tamarugal.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_santiago_centro.xlsx</t>
+  </si>
+  <si>
+    <t>AEL_Valle_Diguillín.xlsx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -952,10 +1063,106 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="22">
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1147,86 +1354,6 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1241,21 +1368,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB655D7C-9877-46E0-92DF-E3EBF603DAAC}" name="Tabla1" displayName="Tabla1" ref="A1:J37" totalsRowShown="0" dataDxfId="10">
-  <autoFilter ref="A1:J37" xr:uid="{FB655D7C-9877-46E0-92DF-E3EBF603DAAC}"/>
-  <tableColumns count="10">
-    <tableColumn id="7" xr3:uid="{81F1FDBA-6F8D-4F84-B350-BE6DAEB4513E}" name="Tipo_SLEP" dataDxfId="9"/>
-    <tableColumn id="1" xr3:uid="{71E197A0-A7D1-4117-A637-141CAE5153C7}" name="SLEP" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{7E154C76-62D9-49AC-8A5C-38CF45CFD1DA}" name="Nombre Completo" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{B28C7421-A9F8-41E9-9CE2-9190783BC6C3}" name="Nombre" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB655D7C-9877-46E0-92DF-E3EBF603DAAC}" name="Tabla1" displayName="Tabla1" ref="A1:K37" totalsRowShown="0" dataDxfId="21">
+  <autoFilter ref="A1:K37" xr:uid="{FB655D7C-9877-46E0-92DF-E3EBF603DAAC}"/>
+  <tableColumns count="11">
+    <tableColumn id="7" xr3:uid="{81F1FDBA-6F8D-4F84-B350-BE6DAEB4513E}" name="Tipo_SLEP" dataDxfId="20"/>
+    <tableColumn id="1" xr3:uid="{71E197A0-A7D1-4117-A637-141CAE5153C7}" name="SLEP" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{7E154C76-62D9-49AC-8A5C-38CF45CFD1DA}" name="Nombre Completo" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{B28C7421-A9F8-41E9-9CE2-9190783BC6C3}" name="Nombre" dataDxfId="17">
       <calculatedColumnFormula>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{894A323A-AFD3-40FD-BB58-2B308B6E9B79}" name="Apellido" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{9E5CEF83-8F1C-47D8-9D60-176E8AC3FEA4}" name="Genero" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{D31AB802-9D0A-47E2-B51A-3E1504C462E0}" name="RUT" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{BFEBADF9-4E36-4F51-BFFE-B6A3E1E4CDC8}" name="correo" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{146F0A02-05F8-4FED-86F3-F5493953AC21}" name="copia" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{6F51BF54-5EDB-4B9D-B425-9871551CED2D}" name="archivo" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{894A323A-AFD3-40FD-BB58-2B308B6E9B79}" name="Apellido" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{9E5CEF83-8F1C-47D8-9D60-176E8AC3FEA4}" name="Genero" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{D31AB802-9D0A-47E2-B51A-3E1504C462E0}" name="RUT" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{BFEBADF9-4E36-4F51-BFFE-B6A3E1E4CDC8}" name="correo" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{146F0A02-05F8-4FED-86F3-F5493953AC21}" name="copia" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{6F51BF54-5EDB-4B9D-B425-9871551CED2D}" name="archivo1" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{EBDDB05A-E9B3-45C9-818B-FD060B42404B}" name="archivo2" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1524,8 +1652,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -1534,9 +1662,10 @@
     <col min="8" max="8" width="40.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.28515625" customWidth="1"/>
     <col min="10" max="10" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1565,1157 +1694,1268 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="C2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Ana</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Ana</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="6" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Eduardo</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="6" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Eduardo</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Jasmín</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Jasmín</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>188</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Jenson</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Juan</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="2" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Juan</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>190</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Yolanda</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>191</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Manuel</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>192</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D9" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>David</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="1" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>193</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D10" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Marcela</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>194</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D11" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Rodrigo</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>195</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D12" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Eugenio</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>196</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Carolina</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>197</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D14" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Ivy</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="1" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>198</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D15" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Mario</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="6" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>199</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="D16" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Sandra</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>200</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D17" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Marcelo</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="1" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
+        <v>201</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D18" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Maryorie</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="1" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>202</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="D19" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Margarita</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="1" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>203</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="D20" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Angeline</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="1" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>204</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="D21" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Daniela</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="1" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>205</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="D22" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Marta</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="1" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>206</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="D23" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Oscar</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="1" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>207</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="D24" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Elena</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="1" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>208</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="D25" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Carolina</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="1" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>209</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="D26" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Tomás</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="1" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>210</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="D27" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Rosita</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Carolina</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Miguel</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Claudia</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Iván</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="I31" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="J31" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="C32" s="3" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="6" t="s">
+      <c r="D32" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Claudio</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="F32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G32" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="H32" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D28" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Carolina</v>
-      </c>
-      <c r="E28" s="4" t="s">
+      <c r="I32" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="7" t="s">
+      <c r="J32" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I28" s="18" t="s">
+      <c r="D33" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Avelino</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="F33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="10" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="H33" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="I33" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="D29" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Miguel</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="J33" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" s="7" t="s">
+      <c r="C34" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="D34" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Emilia</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="I29" s="23" t="s">
+      <c r="F34" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G34" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="H34" s="8" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="6" t="s">
+      <c r="I34" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="J34" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="D30" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Claudia</v>
-      </c>
-      <c r="E30" s="4" t="s">
+      <c r="C35" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="7" t="s">
+      <c r="D35" s="14" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Araceli</v>
+      </c>
+      <c r="E35" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="F35" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G35" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="I30" s="21" t="s">
+      <c r="H35" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="I35" s="24" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" ht="15.75">
-      <c r="A31" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B31" s="6" t="s">
+      <c r="J35" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C36" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="D31" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Iván</v>
-      </c>
-      <c r="E31" s="4" t="s">
+      <c r="D36" s="14" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Natalia</v>
+      </c>
+      <c r="E36" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" s="9" t="s">
+      <c r="F36" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G36" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H36" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="I31" s="18" t="s">
+      <c r="I36" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J36" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" ht="15.75">
-      <c r="A32" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B32" s="6" t="s">
+      <c r="C37" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D37" s="14" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Camila</v>
+      </c>
+      <c r="E37" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="D32" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Claudio</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="F37" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="16" t="s">
+      <c r="H37" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="I37" s="18" t="s">
         <v>184</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D33" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Avelino</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D34" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Emilia</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="I34" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="15.75">
-      <c r="A35" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="D35" s="14" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Araceli</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="I35" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" ht="15.75">
-      <c r="A36" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="D36" s="14" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Natalia</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="I36" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D37" s="14" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Camila</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>220</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>221</v>
       </c>
+      <c r="K37" s="6" t="s">
+        <v>258</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A13 B5:G5 I5 A14:G14 I14">
-    <cfRule type="expression" dxfId="20" priority="2">
+    <cfRule type="expression" dxfId="9" priority="2">
       <formula>$V4=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A25">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="8" priority="1">
       <formula>$V15=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:B3">
-    <cfRule type="expression" dxfId="18" priority="19">
+    <cfRule type="expression" dxfId="7" priority="19">
       <formula>$W3=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:H4">
-    <cfRule type="expression" dxfId="17" priority="18">
+    <cfRule type="expression" dxfId="6" priority="18">
       <formula>$V4=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:H13">
-    <cfRule type="expression" dxfId="16" priority="9">
+    <cfRule type="expression" dxfId="5" priority="9">
       <formula>$V6=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:H25">
-    <cfRule type="expression" dxfId="15" priority="4">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>$V15=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:G2">
-    <cfRule type="expression" dxfId="14" priority="21">
+    <cfRule type="expression" dxfId="3" priority="21">
       <formula>$W2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="expression" dxfId="13" priority="16">
+    <cfRule type="expression" dxfId="2" priority="16">
       <formula>$V5=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I2">
-    <cfRule type="expression" dxfId="12" priority="20">
+    <cfRule type="expression" dxfId="1" priority="20">
       <formula>$W2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25">
-    <cfRule type="expression" dxfId="11" priority="3">
+    <cfRule type="expression" dxfId="0" priority="3">
       <formula>$V25=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2772,136 +3012,136 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16F8E922-1D87-4954-BA47-62B6C3653EB0}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>119</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2913,5 +3153,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BD8AD7E-D7E2-48EE-A5BD-CE862A98C9B8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BD8AD7E-D7E2-48EE-A5BD-CE862A98C9B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/correos/correos_FINAL.xlsx
+++ b/correos/correos_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educacionpublica-my.sharepoint.com/personal/alonso_arrano_dep_cl/Documents/2024/SAE - Anotate en la lista/reporteria_ael/correos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="350" documentId="11_AD4D2F04E46CFB4ACB3E20CA8550FF6C693EDF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{059AF893-8D40-44C5-AEB3-039CA605E834}"/>
+  <xr:revisionPtr revIDLastSave="358" documentId="11_AD4D2F04E46CFB4ACB3E20CA8550FF6C693EDF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1124D927-1FB1-4C5E-9B7C-3198D5E045D6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,6 +69,12 @@
     <t>copia</t>
   </si>
   <si>
+    <t>archivo1</t>
+  </si>
+  <si>
+    <t>archivo2</t>
+  </si>
+  <si>
     <t>Antiguo</t>
   </si>
   <si>
@@ -90,6 +96,12 @@
     <t>jocelyn.almonacid@slepllanquihue.cl</t>
   </si>
   <si>
+    <t>reporte_llanquihue.pdf</t>
+  </si>
+  <si>
+    <t>AEL_llanquihue.xlsx</t>
+  </si>
+  <si>
     <t>Chiloé</t>
   </si>
   <si>
@@ -108,6 +120,12 @@
     <t>Altircio.sarmiento@slepchiloe.gob.cl</t>
   </si>
   <si>
+    <t>reporte_Chiloé.pdf</t>
+  </si>
+  <si>
+    <t>AEL_Chiloé.xlsx</t>
+  </si>
+  <si>
     <t>Valdivia</t>
   </si>
   <si>
@@ -120,6 +138,12 @@
     <t>jasmin.sanmartin@slepvaldivia.gob.cl</t>
   </si>
   <si>
+    <t>reporte_valdivia.pdf</t>
+  </si>
+  <si>
+    <t>AEL_valdivia.xlsx</t>
+  </si>
+  <si>
     <t>Santa Rosa</t>
   </si>
   <si>
@@ -135,6 +159,12 @@
     <t>josefina.abarzua@slepsantarosa.gob.cl</t>
   </si>
   <si>
+    <t>reporte_santa_rosa.pdf</t>
+  </si>
+  <si>
+    <t>AEL_santa_rosa.xlsx</t>
+  </si>
+  <si>
     <t>Santa Corina</t>
   </si>
   <si>
@@ -147,6 +177,12 @@
     <t>juan.duran@slepsantacorina.gob.cl</t>
   </si>
   <si>
+    <t>reporte_santa_corina.pdf</t>
+  </si>
+  <si>
+    <t>AEL_santa_corina.xlsx</t>
+  </si>
+  <si>
     <t>Maule Costa</t>
   </si>
   <si>
@@ -159,6 +195,12 @@
     <t>yolanda.urrutia@slepmaulecosta.gob.cl</t>
   </si>
   <si>
+    <t>reporte_maule_costa.pdf</t>
+  </si>
+  <si>
+    <t>AEL_maule_costa.xlsx</t>
+  </si>
+  <si>
     <t>Los Libertadores</t>
   </si>
   <si>
@@ -171,6 +213,12 @@
     <t>manuel.coloma@sleploslibertadores.gob.cl</t>
   </si>
   <si>
+    <t>reporte_los_libertadores.pdf</t>
+  </si>
+  <si>
+    <t>AEL_los_libertadores.xlsx</t>
+  </si>
+  <si>
     <t>Licancabur</t>
   </si>
   <si>
@@ -183,6 +231,12 @@
     <t>david.cruz@sleplicancabur.cl</t>
   </si>
   <si>
+    <t>reporte_licancabur.pdf</t>
+  </si>
+  <si>
+    <t>AEL_licancabur.xlsx</t>
+  </si>
+  <si>
     <t>Andalién Costa</t>
   </si>
   <si>
@@ -198,6 +252,12 @@
     <t>marcela.valencia@slepandaliencosta.gob.cl</t>
   </si>
   <si>
+    <t>reporte_andalién_costa.pdf</t>
+  </si>
+  <si>
+    <t>AEL_andalién_costa.xlsx</t>
+  </si>
+  <si>
     <t>Del Pino</t>
   </si>
   <si>
@@ -210,6 +270,12 @@
     <t>rodrigo.yanez@edudelpino.gob.cl</t>
   </si>
   <si>
+    <t>reporte_del_pino.pdf</t>
+  </si>
+  <si>
+    <t>AEL_del_pino.xlsx</t>
+  </si>
+  <si>
     <t>Punilla Cordillera</t>
   </si>
   <si>
@@ -225,6 +291,12 @@
     <t>karla.sepulveda@sleppunillacordillera.cl</t>
   </si>
   <si>
+    <t>reporte_punilla_cordillera.pdf</t>
+  </si>
+  <si>
+    <t>AEL_punilla_cordillera.xlsx</t>
+  </si>
+  <si>
     <t>Magallanes</t>
   </si>
   <si>
@@ -237,6 +309,12 @@
     <t>carolina.figueroa@slepmagallanes.cl</t>
   </si>
   <si>
+    <t>reporte_magallanes.pdf</t>
+  </si>
+  <si>
+    <t>AEL_magallanes.xlsx</t>
+  </si>
+  <si>
     <t>Aysen</t>
   </si>
   <si>
@@ -252,6 +330,12 @@
     <t>freddy.moraga@slepaysen.cl</t>
   </si>
   <si>
+    <t>reporte_aysén.pdf</t>
+  </si>
+  <si>
+    <t>AEL_aysén.xlsx</t>
+  </si>
+  <si>
     <t xml:space="preserve">Iquique </t>
   </si>
   <si>
@@ -264,6 +348,12 @@
     <t>mario.reyes@slepiquique.cl</t>
   </si>
   <si>
+    <t>reporte_iquique.pdf</t>
+  </si>
+  <si>
+    <t>AEL_iquique.xlsx</t>
+  </si>
+  <si>
     <t>Costa Araucanía</t>
   </si>
   <si>
@@ -276,6 +366,12 @@
     <t>sandra.padilla@slepca.cl</t>
   </si>
   <si>
+    <t>reporte_costa_araucanía.pdf</t>
+  </si>
+  <si>
+    <t>AEL_costa_araucanía.xlsx</t>
+  </si>
+  <si>
     <t xml:space="preserve">Atacama </t>
   </si>
   <si>
@@ -288,6 +384,12 @@
     <t>marcelo.quiroga@slepatacama.cl</t>
   </si>
   <si>
+    <t>reporte_atacama.pdf</t>
+  </si>
+  <si>
+    <t>AEL_atacama.xlsx</t>
+  </si>
+  <si>
     <t>Huasco</t>
   </si>
   <si>
@@ -300,6 +402,12 @@
     <t>maryorie.alquinta@slephuasco.cl</t>
   </si>
   <si>
+    <t>reporte_huasco.pdf</t>
+  </si>
+  <si>
+    <t>AEL_huasco.xlsx</t>
+  </si>
+  <si>
     <t>Puerto Cordillera</t>
   </si>
   <si>
@@ -312,6 +420,12 @@
     <t>margarita.campillo@slepuertocordillera.cl</t>
   </si>
   <si>
+    <t>reporte_puerto_cordillera.pdf</t>
+  </si>
+  <si>
+    <t>AEL_puerto_cordillera.xlsx</t>
+  </si>
+  <si>
     <t>Valparaíso</t>
   </si>
   <si>
@@ -324,6 +438,12 @@
     <t>angeline.castillo@slepvalparaiso.cl</t>
   </si>
   <si>
+    <t>reporte_valparaíso.pdf</t>
+  </si>
+  <si>
+    <t>AEL_valparaíso.xlsx</t>
+  </si>
+  <si>
     <t>Barrancas</t>
   </si>
   <si>
@@ -336,6 +456,12 @@
     <t>daniela.chamorro@slepb.cl</t>
   </si>
   <si>
+    <t>reporte_barrancas.pdf</t>
+  </si>
+  <si>
+    <t>AEL_barrancas.xlsx</t>
+  </si>
+  <si>
     <t>Gabriela Mistral</t>
   </si>
   <si>
@@ -348,6 +474,12 @@
     <t>marta.hinojosa@slepgm.cl</t>
   </si>
   <si>
+    <t>reporte_gabriela_mistral.pdf</t>
+  </si>
+  <si>
+    <t>AEL_gabriela_mistral.xlsx</t>
+  </si>
+  <si>
     <t>Colchagua</t>
   </si>
   <si>
@@ -360,6 +492,12 @@
     <t>oscar.ubilla@slepcolchagua.cl</t>
   </si>
   <si>
+    <t>reporte_colchagua.pdf</t>
+  </si>
+  <si>
+    <t>AEL_colchagua.xlsx</t>
+  </si>
+  <si>
     <t>Andalién Sur</t>
   </si>
   <si>
@@ -372,6 +510,12 @@
     <t>elena.saez@andaliensur.cl</t>
   </si>
   <si>
+    <t>reporte_andalién_sur.pdf</t>
+  </si>
+  <si>
+    <t>AEL_andalién_sur.xlsx</t>
+  </si>
+  <si>
     <t>Chinchorro</t>
   </si>
   <si>
@@ -387,6 +531,12 @@
     <t>shirley.villegas@epchinchorro.cl</t>
   </si>
   <si>
+    <t>reporte_chinchorro.pdf</t>
+  </si>
+  <si>
+    <t>AEL_chinchorro.xlsx</t>
+  </si>
+  <si>
     <t>Costa Central</t>
   </si>
   <si>
@@ -399,6 +549,12 @@
     <t>tomas.gonzalez@slepcostacentral.gob.cl</t>
   </si>
   <si>
+    <t>reporte_costa_central.pdf</t>
+  </si>
+  <si>
+    <t>AEL_costa_central.xlsx</t>
+  </si>
+  <si>
     <t>Elqui</t>
   </si>
   <si>
@@ -414,6 +570,12 @@
     <t>marco.vega@slepelqui.gob.cl</t>
   </si>
   <si>
+    <t>reporte_elqui.pdf</t>
+  </si>
+  <si>
+    <t>AEL_elqui.xlsx</t>
+  </si>
+  <si>
     <t>Nuevo</t>
   </si>
   <si>
@@ -435,6 +597,12 @@
     <t>mauricio.urrutia@sleppetorca.gob.cl</t>
   </si>
   <si>
+    <t>reporte_petorca.pdf</t>
+  </si>
+  <si>
+    <t>AEL_petorca.xlsx</t>
+  </si>
+  <si>
     <t>Los Andes</t>
   </si>
   <si>
@@ -453,6 +621,12 @@
     <t>felipe.martinez@sleplosandes.gob.cl</t>
   </si>
   <si>
+    <t>reporte_los_andes.pdf</t>
+  </si>
+  <si>
+    <t>AEL_los_andes.xlsx</t>
+  </si>
+  <si>
     <t>Aconcagua</t>
   </si>
   <si>
@@ -471,24 +645,36 @@
     <t>yasna.flos@slepaconcagua.gob.cl</t>
   </si>
   <si>
+    <t>reporte_aconcagua.pdf</t>
+  </si>
+  <si>
+    <t>AEL_aconcagua.xlsx</t>
+  </si>
+  <si>
     <t>Puelche</t>
   </si>
   <si>
-    <t>Iván Alejandro Ramírez Hidalgo</t>
-  </si>
-  <si>
-    <t>Ramírez</t>
-  </si>
-  <si>
-    <t>9.488.256-7</t>
-  </si>
-  <si>
-    <t>Ivan.ramirez@sleppuelche.gob.cl</t>
+    <t>Jean Carlos Danilo Franco Parra</t>
+  </si>
+  <si>
+    <t>Franco</t>
+  </si>
+  <si>
+    <t>13.386.350-8</t>
+  </si>
+  <si>
+    <t>Jean.franco@sleppuelche.gob.cl</t>
   </si>
   <si>
     <t>rossemarie.sanchez@sleppuelche.gob.cl</t>
   </si>
   <si>
+    <t>reporte_puelche.pdf</t>
+  </si>
+  <si>
+    <t>AEL_puelche.xlsx</t>
+  </si>
+  <si>
     <t>Los Álamos</t>
   </si>
   <si>
@@ -507,6 +693,12 @@
     <t>ximena.valenzuela@sleplosalamos.gob.cl</t>
   </si>
   <si>
+    <t>reporte_los_álamos.pdf</t>
+  </si>
+  <si>
+    <t>AEL_los_álamos.xlsx</t>
+  </si>
+  <si>
     <t>Marga Marga</t>
   </si>
   <si>
@@ -525,6 +717,12 @@
     <t>jorge.manchini@slepmargamarga.gob.cl</t>
   </si>
   <si>
+    <t>reporte_marga_marga.pdf</t>
+  </si>
+  <si>
+    <t>AEL_marga_marga.xlsx</t>
+  </si>
+  <si>
     <t>Los Parques</t>
   </si>
   <si>
@@ -543,6 +741,12 @@
     <t>flavia.fiabane@sleplosparques.gob.cl</t>
   </si>
   <si>
+    <t>reporte_los_parques.pdf</t>
+  </si>
+  <si>
+    <t>AEL_los_parques.xlsx</t>
+  </si>
+  <si>
     <t>Tamarugal</t>
   </si>
   <si>
@@ -561,6 +765,12 @@
     <t>samuel.diaz@sleptamarugal.gob.cl</t>
   </si>
   <si>
+    <t>reporte_tamarugal.pdf</t>
+  </si>
+  <si>
+    <t>AEL_tamarugal.xlsx</t>
+  </si>
+  <si>
     <t>Santiago Centro</t>
   </si>
   <si>
@@ -579,6 +789,12 @@
     <t>juan.saez@slepsantiagocentro.gob.cl</t>
   </si>
   <si>
+    <t>reporte_santiago_centro.pdf</t>
+  </si>
+  <si>
+    <t>AEL_santiago_centro.xlsx</t>
+  </si>
+  <si>
     <t>Valle Diguillín</t>
   </si>
   <si>
@@ -597,223 +813,7 @@
     <t>sergio.hernandez@slepvallediguillin.gob.cl</t>
   </si>
   <si>
-    <t>archivo1</t>
-  </si>
-  <si>
-    <t>reporte_llanquihue.pdf</t>
-  </si>
-  <si>
-    <t>reporte_Chiloé.pdf</t>
-  </si>
-  <si>
-    <t>reporte_valdivia.pdf</t>
-  </si>
-  <si>
-    <t>reporte_santa_rosa.pdf</t>
-  </si>
-  <si>
-    <t>reporte_santa_corina.pdf</t>
-  </si>
-  <si>
-    <t>reporte_maule_costa.pdf</t>
-  </si>
-  <si>
-    <t>reporte_los_libertadores.pdf</t>
-  </si>
-  <si>
-    <t>reporte_licancabur.pdf</t>
-  </si>
-  <si>
-    <t>reporte_andalién_costa.pdf</t>
-  </si>
-  <si>
-    <t>reporte_del_pino.pdf</t>
-  </si>
-  <si>
-    <t>reporte_punilla_cordillera.pdf</t>
-  </si>
-  <si>
-    <t>reporte_magallanes.pdf</t>
-  </si>
-  <si>
-    <t>reporte_aysén.pdf</t>
-  </si>
-  <si>
-    <t>reporte_iquique.pdf</t>
-  </si>
-  <si>
-    <t>reporte_costa_araucanía.pdf</t>
-  </si>
-  <si>
-    <t>reporte_atacama.pdf</t>
-  </si>
-  <si>
-    <t>reporte_huasco.pdf</t>
-  </si>
-  <si>
-    <t>reporte_puerto_cordillera.pdf</t>
-  </si>
-  <si>
-    <t>reporte_valparaíso.pdf</t>
-  </si>
-  <si>
-    <t>reporte_barrancas.pdf</t>
-  </si>
-  <si>
-    <t>reporte_gabriela_mistral.pdf</t>
-  </si>
-  <si>
-    <t>reporte_colchagua.pdf</t>
-  </si>
-  <si>
-    <t>reporte_andalién_sur.pdf</t>
-  </si>
-  <si>
-    <t>reporte_chinchorro.pdf</t>
-  </si>
-  <si>
-    <t>reporte_costa_central.pdf</t>
-  </si>
-  <si>
-    <t>reporte_elqui.pdf</t>
-  </si>
-  <si>
-    <t>reporte_petorca.pdf</t>
-  </si>
-  <si>
-    <t>reporte_los_andes.pdf</t>
-  </si>
-  <si>
-    <t>reporte_aconcagua.pdf</t>
-  </si>
-  <si>
-    <t>reporte_puelche.pdf</t>
-  </si>
-  <si>
-    <t>reporte_los_álamos.pdf</t>
-  </si>
-  <si>
-    <t>reporte_marga_marga.pdf</t>
-  </si>
-  <si>
-    <t>reporte_los_parques.pdf</t>
-  </si>
-  <si>
-    <t>reporte_tamarugal.pdf</t>
-  </si>
-  <si>
-    <t>reporte_santiago_centro.pdf</t>
-  </si>
-  <si>
     <t>reporte_Valle_Diguillín.pdf</t>
-  </si>
-  <si>
-    <t>archivo2</t>
-  </si>
-  <si>
-    <t>AEL_llanquihue.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_Chiloé.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_valdivia.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_santa_rosa.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_santa_corina.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_maule_costa.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_los_libertadores.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_licancabur.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_andalién_costa.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_del_pino.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_punilla_cordillera.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_magallanes.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_aysén.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_iquique.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_costa_araucanía.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_atacama.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_huasco.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_puerto_cordillera.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_valparaíso.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_barrancas.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_gabriela_mistral.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_colchagua.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_andalién_sur.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_chinchorro.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_costa_central.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_elqui.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_petorca.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_los_andes.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_aconcagua.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_puelche.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_los_álamos.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_marga_marga.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_los_parques.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_tamarugal.xlsx</t>
-  </si>
-  <si>
-    <t>AEL_santiago_centro.xlsx</t>
   </si>
   <si>
     <t>AEL_Valle_Diguillín.xlsx</t>
@@ -823,7 +823,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1063,90 +1063,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="gray125">
-          <fgColor theme="9" tint="0.39994506668294322"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1354,6 +1274,86 @@
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="gray125">
+          <fgColor theme="9" tint="0.39994506668294322"/>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1368,22 +1368,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB655D7C-9877-46E0-92DF-E3EBF603DAAC}" name="Tabla1" displayName="Tabla1" ref="A1:K37" totalsRowShown="0" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB655D7C-9877-46E0-92DF-E3EBF603DAAC}" name="Tabla1" displayName="Tabla1" ref="A1:K37" totalsRowShown="0" dataDxfId="11">
   <autoFilter ref="A1:K37" xr:uid="{FB655D7C-9877-46E0-92DF-E3EBF603DAAC}"/>
   <tableColumns count="11">
-    <tableColumn id="7" xr3:uid="{81F1FDBA-6F8D-4F84-B350-BE6DAEB4513E}" name="Tipo_SLEP" dataDxfId="20"/>
-    <tableColumn id="1" xr3:uid="{71E197A0-A7D1-4117-A637-141CAE5153C7}" name="SLEP" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{7E154C76-62D9-49AC-8A5C-38CF45CFD1DA}" name="Nombre Completo" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{B28C7421-A9F8-41E9-9CE2-9190783BC6C3}" name="Nombre" dataDxfId="17">
+    <tableColumn id="7" xr3:uid="{81F1FDBA-6F8D-4F84-B350-BE6DAEB4513E}" name="Tipo_SLEP" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{71E197A0-A7D1-4117-A637-141CAE5153C7}" name="SLEP" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{7E154C76-62D9-49AC-8A5C-38CF45CFD1DA}" name="Nombre Completo" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{B28C7421-A9F8-41E9-9CE2-9190783BC6C3}" name="Nombre" dataDxfId="7">
       <calculatedColumnFormula>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{894A323A-AFD3-40FD-BB58-2B308B6E9B79}" name="Apellido" dataDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{9E5CEF83-8F1C-47D8-9D60-176E8AC3FEA4}" name="Genero" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{D31AB802-9D0A-47E2-B51A-3E1504C462E0}" name="RUT" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{BFEBADF9-4E36-4F51-BFFE-B6A3E1E4CDC8}" name="correo" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{146F0A02-05F8-4FED-86F3-F5493953AC21}" name="copia" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{6F51BF54-5EDB-4B9D-B425-9871551CED2D}" name="archivo1" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{EBDDB05A-E9B3-45C9-818B-FD060B42404B}" name="archivo2" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{894A323A-AFD3-40FD-BB58-2B308B6E9B79}" name="Apellido" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{9E5CEF83-8F1C-47D8-9D60-176E8AC3FEA4}" name="Genero" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{D31AB802-9D0A-47E2-B51A-3E1504C462E0}" name="RUT" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{BFEBADF9-4E36-4F51-BFFE-B6A3E1E4CDC8}" name="correo" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{146F0A02-05F8-4FED-86F3-F5493953AC21}" name="copia" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{6F51BF54-5EDB-4B9D-B425-9871551CED2D}" name="archivo1" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{EBDDB05A-E9B3-45C9-818B-FD060B42404B}" name="archivo2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1653,7 +1653,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
@@ -1665,7 +1665,7 @@
     <col min="11" max="11" width="29.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1694,1215 +1694,1215 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>185</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Ana</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>186</v>
+        <v>18</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" s="6" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Eduardo</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="6" t="s">
-        <v>187</v>
+        <v>26</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D4" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Jasmín</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6" t="s">
-        <v>188</v>
+        <v>32</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Jenson</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>189</v>
+        <v>39</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Juan</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="6" t="s">
-        <v>190</v>
+        <v>45</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Yolanda</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6" t="s">
-        <v>191</v>
+        <v>51</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Manuel</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="1" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
-        <v>192</v>
+        <v>57</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D9" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>David</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="1" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
-        <v>193</v>
+        <v>63</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D10" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Marcela</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>194</v>
+        <v>70</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D11" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Rodrigo</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="D12" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Eugenio</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="1" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>196</v>
+        <v>83</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="D13" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Carolina</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="1" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D14" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Ivy</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="1" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="D15" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Mario</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="1" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="6" t="s">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="D16" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Sandra</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="1" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="6" t="s">
-        <v>200</v>
+        <v>108</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="D17" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Marcelo</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="1" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="D18" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Maryorie</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="1" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="D19" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Margarita</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="1" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="I19" s="6"/>
       <c r="J19" s="6" t="s">
-        <v>203</v>
+        <v>126</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="D20" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Angeline</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="1" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="6" t="s">
-        <v>204</v>
+        <v>132</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="D21" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Daniela</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="1" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="6" t="s">
-        <v>205</v>
+        <v>138</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="D22" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Marta</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="1" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="D23" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Oscar</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="1" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="6" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="D24" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Elena</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>108</v>
+        <v>154</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="1" t="s">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="6" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>110</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Carolina</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="1" t="s">
-        <v>113</v>
+        <v>161</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>114</v>
+        <v>162</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>209</v>
+        <v>163</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="D26" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Tomás</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>117</v>
+        <v>167</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="1" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="6" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="D27" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Rosita</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="1" t="s">
-        <v>122</v>
+        <v>174</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>123</v>
+        <v>175</v>
       </c>
       <c r="J27" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Carolina</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I28" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D29" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Miguel</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Claudia</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15.75">
+      <c r="A31" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D31" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Jean</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="I31" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15.75">
+      <c r="A32" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="C32" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D32" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Claudio</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D33" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Avelino</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I33" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="D34" s="4" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Emilia</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>232</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15.75">
+      <c r="A35" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D35" s="14" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Araceli</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="I35" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15.75">
+      <c r="A36" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="D36" s="14" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Natalia</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="I36" s="18" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Carolina</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I28" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="K28" s="6" t="s">
+      <c r="J36" s="6" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D29" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Miguel</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="K29" s="6" t="s">
+      <c r="K36" s="6" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D30" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Claudia</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="K30" s="6" t="s">
+    <row r="37" spans="1:11">
+      <c r="A37" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Iván</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="H31" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="I31" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="K31" s="6" t="s">
+      <c r="C37" s="13" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D32" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Claudio</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K32" s="6" t="s">
+      <c r="D37" s="14" t="str">
+        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
+        <v>Camila</v>
+      </c>
+      <c r="E37" s="14" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D33" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Avelino</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="I33" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="K33" s="6" t="s">
+      <c r="F37" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="6" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D34" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Emilia</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="I34" s="20" t="s">
-        <v>166</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="K34" s="6" t="s">
+      <c r="H37" s="12" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="D35" s="14" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Araceli</v>
-      </c>
-      <c r="E35" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="F35" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="H35" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="I35" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="K35" s="6" t="s">
+      <c r="I37" s="18" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="D36" s="14" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Natalia</v>
-      </c>
-      <c r="E36" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="I36" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="K36" s="6" t="s">
+      <c r="J37" s="6" t="s">
         <v>257</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D37" s="14" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Camila</v>
-      </c>
-      <c r="E37" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="F37" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="H37" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="I37" s="18" t="s">
-        <v>184</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>221</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>258</v>
@@ -2910,52 +2910,52 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A13 B5:G5 I5 A14:G14 I14">
-    <cfRule type="expression" dxfId="9" priority="2">
+    <cfRule type="expression" dxfId="21" priority="2">
       <formula>$V4=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A15:A25">
-    <cfRule type="expression" dxfId="8" priority="1">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>$V15=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3:B3">
-    <cfRule type="expression" dxfId="7" priority="19">
+    <cfRule type="expression" dxfId="19" priority="19">
       <formula>$W3=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:H4">
-    <cfRule type="expression" dxfId="6" priority="18">
+    <cfRule type="expression" dxfId="18" priority="18">
       <formula>$V4=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B6:H13">
-    <cfRule type="expression" dxfId="5" priority="9">
+    <cfRule type="expression" dxfId="17" priority="9">
       <formula>$V6=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:H25">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="16" priority="4">
       <formula>$V15=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:G2">
-    <cfRule type="expression" dxfId="3" priority="21">
+    <cfRule type="expression" dxfId="15" priority="21">
       <formula>$W2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="expression" dxfId="2" priority="16">
+    <cfRule type="expression" dxfId="14" priority="16">
       <formula>$V5=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I2">
-    <cfRule type="expression" dxfId="1" priority="20">
+    <cfRule type="expression" dxfId="13" priority="20">
       <formula>$W2=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I25">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="12" priority="3">
       <formula>$V25=1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2992,14 +2992,14 @@
     <hyperlink ref="I37" r:id="rId30" xr:uid="{8A354AB1-E770-4F79-B1BA-93ADD65AA4C2}"/>
     <hyperlink ref="I28" r:id="rId31" xr:uid="{874DA179-19F1-4B04-84DB-71FE5C56F6F3}"/>
     <hyperlink ref="I31" r:id="rId32" xr:uid="{23A89A35-5FE5-4753-8C1C-C063A7CCAF17}"/>
-    <hyperlink ref="H31" r:id="rId33" xr:uid="{8CE3801F-2D31-452D-923C-A8593A3AA3A3}"/>
-    <hyperlink ref="H36" r:id="rId34" xr:uid="{5E6E2E2A-9007-46B7-9964-2E09249D8F3A}"/>
-    <hyperlink ref="I34" r:id="rId35" xr:uid="{0011810F-DE97-45D0-9471-2DE01C3A5189}"/>
-    <hyperlink ref="I30" r:id="rId36" xr:uid="{A7A1E120-0ED5-475C-A8BB-BE81B51B7066}"/>
-    <hyperlink ref="I32" r:id="rId37" xr:uid="{301B3643-4756-45C1-BC55-FF9FD4821B41}"/>
-    <hyperlink ref="I29" r:id="rId38" xr:uid="{129AB270-59C0-4501-B6EC-9626D7FC587B}"/>
-    <hyperlink ref="I33" r:id="rId39" xr:uid="{9621396B-EE77-4EC0-85EA-D9CF2492F76D}"/>
-    <hyperlink ref="I35" r:id="rId40" xr:uid="{7B46DDAA-2840-4B7C-806A-9D8C13D76907}"/>
+    <hyperlink ref="H36" r:id="rId33" xr:uid="{5E6E2E2A-9007-46B7-9964-2E09249D8F3A}"/>
+    <hyperlink ref="I34" r:id="rId34" xr:uid="{0011810F-DE97-45D0-9471-2DE01C3A5189}"/>
+    <hyperlink ref="I30" r:id="rId35" xr:uid="{A7A1E120-0ED5-475C-A8BB-BE81B51B7066}"/>
+    <hyperlink ref="I32" r:id="rId36" xr:uid="{301B3643-4756-45C1-BC55-FF9FD4821B41}"/>
+    <hyperlink ref="I29" r:id="rId37" xr:uid="{129AB270-59C0-4501-B6EC-9626D7FC587B}"/>
+    <hyperlink ref="I33" r:id="rId38" xr:uid="{9621396B-EE77-4EC0-85EA-D9CF2492F76D}"/>
+    <hyperlink ref="I35" r:id="rId39" xr:uid="{7B46DDAA-2840-4B7C-806A-9D8C13D76907}"/>
+    <hyperlink ref="H31" r:id="rId40" xr:uid="{FAA28E75-E2F4-4BCF-9A90-108B43017BBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" verticalDpi="0" r:id="rId41"/>
@@ -3012,136 +3012,136 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16F8E922-1D87-4954-BA47-62B6C3653EB0}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3153,9 +3153,5 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BD8AD7E-D7E2-48EE-A5BD-CE862A98C9B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BD8AD7E-D7E2-48EE-A5BD-CE862A98C9B8}"/>
 </file>
--- a/correos/correos_FINAL.xlsx
+++ b/correos/correos_FINAL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educacionpublica-my.sharepoint.com/personal/alonso_arrano_dep_cl/Documents/2024/SAE - Anotate en la lista/reporteria_ael/correos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="358" documentId="11_AD4D2F04E46CFB4ACB3E20CA8550FF6C693EDF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1124D927-1FB1-4C5E-9B7C-3198D5E045D6}"/>
+  <xr:revisionPtr revIDLastSave="386" documentId="11_AD4D2F04E46CFB4ACB3E20CA8550FF6C693EDF25" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CB5868B-1C2F-4520-8FF1-445445B6A495}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="260">
   <si>
     <t>Tipo_SLEP</t>
   </si>
@@ -177,6 +177,9 @@
     <t>juan.duran@slepsantacorina.gob.cl</t>
   </si>
   <si>
+    <t>pablo.aguero@slepsantacorina.gob.cl</t>
+  </si>
+  <si>
     <t>reporte_santa_corina.pdf</t>
   </si>
   <si>
@@ -411,13 +414,13 @@
     <t>Puerto Cordillera</t>
   </si>
   <si>
-    <t>Margarita Campillo</t>
-  </si>
-  <si>
-    <t>Campillo</t>
-  </si>
-  <si>
-    <t>margarita.campillo@slepuertocordillera.cl</t>
+    <t>Angélica Pizarro</t>
+  </si>
+  <si>
+    <t>Pizarro</t>
+  </si>
+  <si>
+    <t>apizarro.0361@slepuertocordillera.cl</t>
   </si>
   <si>
     <t>reporte_puerto_cordillera.pdf</t>
@@ -582,19 +585,19 @@
     <t>Petorca</t>
   </si>
   <si>
-    <t>Carolina Villagra Marín </t>
-  </si>
-  <si>
-    <t>Villagra</t>
-  </si>
-  <si>
-    <t>18.064.502-0</t>
+    <t>Mauricio Urrutia</t>
+  </si>
+  <si>
+    <t>Mauricio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urrutia </t>
+  </si>
+  <si>
+    <t>mauricio.urrutia@sleppetorca.gob.cl</t>
   </si>
   <si>
     <t>carolina.villagra@sleppetorca.gob.cl </t>
-  </si>
-  <si>
-    <t>mauricio.urrutia@sleppetorca.gob.cl</t>
   </si>
   <si>
     <t>reporte_petorca.pdf</t>
@@ -911,7 +914,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -994,12 +997,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1059,6 +1073,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1652,7 +1669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -1834,7 +1851,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" ht="15.75">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
@@ -1858,12 +1875,14 @@
       <c r="H6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="6"/>
+      <c r="I6" s="19" t="s">
+        <v>45</v>
+      </c>
       <c r="J6" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1871,31 +1890,31 @@
         <v>11</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Yolanda</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1903,31 +1922,31 @@
         <v>11</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Manuel</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1935,31 +1954,31 @@
         <v>11</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>David</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I9" s="6"/>
       <c r="J9" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1967,33 +1986,33 @@
         <v>11</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Marcela</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I10" s="6"/>
       <c r="J10" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2001,31 +2020,31 @@
         <v>11</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Rodrigo</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2033,33 +2052,33 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Eugenio</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2067,31 +2086,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Carolina</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I13" s="6"/>
       <c r="J13" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2099,33 +2118,33 @@
         <v>11</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Ivy</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2133,31 +2152,31 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D15" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Mario</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2165,31 +2184,31 @@
         <v>11</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D16" s="2" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Sandra</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2197,31 +2216,31 @@
         <v>11</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D17" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Marcelo</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I17" s="6"/>
       <c r="J17" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2229,31 +2248,31 @@
         <v>11</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D18" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Maryorie</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2261,31 +2280,33 @@
         <v>11</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D19" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Margarita</v>
+        <v>Angélica</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="3"/>
-      <c r="H19" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I19" s="6"/>
+      <c r="H19" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="I19" s="18" t="s">
+        <v>126</v>
+      </c>
       <c r="J19" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2293,31 +2314,31 @@
         <v>11</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D20" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Angeline</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I20" s="6"/>
       <c r="J20" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2325,31 +2346,31 @@
         <v>11</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D21" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Daniela</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I21" s="6"/>
       <c r="J21" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2357,31 +2378,31 @@
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D22" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Marta</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I22" s="6"/>
       <c r="J22" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2389,31 +2410,31 @@
         <v>11</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D23" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Oscar</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I23" s="6"/>
       <c r="J23" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2421,31 +2442,31 @@
         <v>11</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D24" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Elena</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2453,33 +2474,33 @@
         <v>11</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D25" s="3" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Carolina</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2487,31 +2508,31 @@
         <v>11</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D26" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Tomás</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2519,394 +2540,394 @@
         <v>11</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D27" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Rosita</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D28" s="4" t="str">
-        <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
-        <v>Carolina</v>
+        <v>181</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>182</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I28" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="7"/>
+      <c r="H28" s="18" t="s">
         <v>184</v>
       </c>
+      <c r="I28" s="25" t="s">
+        <v>185</v>
+      </c>
       <c r="J28" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D29" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Miguel</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D30" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Claudia</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I30" s="21" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15.75">
       <c r="A31" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D31" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Jean</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75">
       <c r="A32" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D32" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Claudio</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I32" s="22" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D33" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Avelino</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>23</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I33" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D34" s="4" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Emilia</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>15</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="15.75">
       <c r="A35" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D35" s="14" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Araceli</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I35" s="24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="15.75">
       <c r="A36" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D36" s="14" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Natalia</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G36" s="19" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I36" s="18" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D37" s="14" t="str">
         <f>LEFT(Tabla1[[#This Row],[Nombre Completo]],SEARCH(" ",Tabla1[[#This Row],[Nombre Completo]],1)-1)</f>
         <v>Camila</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F37" s="14" t="s">
         <v>15</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I37" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>258</v>
-      </c>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="H39" s="25"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A4:A13 B5:G5 I5 A14:G14 I14">
@@ -2934,7 +2955,7 @@
       <formula>$V6=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B15:H25">
+  <conditionalFormatting sqref="B15:H18 B20:H25 B19:G19">
     <cfRule type="expression" dxfId="16" priority="4">
       <formula>$V15=1</formula>
     </cfRule>
@@ -2973,38 +2994,39 @@
     <hyperlink ref="H16" r:id="rId11" xr:uid="{AEDEA0EB-604C-4C31-9304-42A01F8A5A3D}"/>
     <hyperlink ref="H18" r:id="rId12" xr:uid="{F7398C85-77F6-4B2F-90F2-2305F57C2050}"/>
     <hyperlink ref="H17" r:id="rId13" xr:uid="{5716803F-2B2A-4A17-BB69-8FDFE706A2AB}"/>
-    <hyperlink ref="H19" r:id="rId14" xr:uid="{E9048617-0AB9-404F-AD37-74E9A485BE30}"/>
-    <hyperlink ref="H20" r:id="rId15" xr:uid="{E454A7F1-60B0-46A2-BCAF-6EE451073594}"/>
-    <hyperlink ref="H21" r:id="rId16" xr:uid="{1127AC0B-364E-4EAD-9D99-A94EA5C42523}"/>
-    <hyperlink ref="H22" r:id="rId17" xr:uid="{898CFB37-C10F-4164-9DC8-B35726F71024}"/>
-    <hyperlink ref="H23" r:id="rId18" xr:uid="{9ECCB776-E8C3-4105-A6F7-2E6F2A184663}"/>
-    <hyperlink ref="H24" r:id="rId19" xr:uid="{4FC5ADBE-181E-43FF-9751-D6D427F0366F}"/>
-    <hyperlink ref="H25" r:id="rId20" xr:uid="{8A1E636A-763E-4FEA-AA46-C17108413427}"/>
-    <hyperlink ref="I25" r:id="rId21" xr:uid="{BC1D1921-7D71-457C-A023-855DF7FD4289}"/>
-    <hyperlink ref="H28" r:id="rId22" display="mailto:carolina.villagra@sleppetorca.gob.cl" xr:uid="{FA5AB3B0-F9E2-45ED-820A-9057AA7CB237}"/>
-    <hyperlink ref="H30" r:id="rId23" display="mailto:claudia.cubillos@slepaconcagua.gob.cl" xr:uid="{BF5D4A03-B565-4290-A323-81DEBCE5CFFB}"/>
-    <hyperlink ref="H32" r:id="rId24" display="mailto:claudio.wilson@sleplosalamos.gob.cl" xr:uid="{75417199-A8F7-4F2B-95A4-F7A17C2548B4}"/>
-    <hyperlink ref="H33" r:id="rId25" xr:uid="{54980B47-C332-416B-B63C-509B623066BB}"/>
-    <hyperlink ref="H34" r:id="rId26" xr:uid="{EA77E657-6305-4130-AE9B-9278175D24E4}"/>
-    <hyperlink ref="H35" r:id="rId27" display="mailto:araceli.nunez@sleptamarugal.gob.cl" xr:uid="{A213DA54-6A21-4C6A-BAD1-5943AE13A95A}"/>
-    <hyperlink ref="I36" r:id="rId28" xr:uid="{A0920DFD-228F-41BB-9846-5BA8CD1645DD}"/>
-    <hyperlink ref="H37" r:id="rId29" xr:uid="{47683FAC-4633-465C-A962-957D7E10B3B6}"/>
-    <hyperlink ref="I37" r:id="rId30" xr:uid="{8A354AB1-E770-4F79-B1BA-93ADD65AA4C2}"/>
-    <hyperlink ref="I28" r:id="rId31" xr:uid="{874DA179-19F1-4B04-84DB-71FE5C56F6F3}"/>
-    <hyperlink ref="I31" r:id="rId32" xr:uid="{23A89A35-5FE5-4753-8C1C-C063A7CCAF17}"/>
-    <hyperlink ref="H36" r:id="rId33" xr:uid="{5E6E2E2A-9007-46B7-9964-2E09249D8F3A}"/>
-    <hyperlink ref="I34" r:id="rId34" xr:uid="{0011810F-DE97-45D0-9471-2DE01C3A5189}"/>
-    <hyperlink ref="I30" r:id="rId35" xr:uid="{A7A1E120-0ED5-475C-A8BB-BE81B51B7066}"/>
-    <hyperlink ref="I32" r:id="rId36" xr:uid="{301B3643-4756-45C1-BC55-FF9FD4821B41}"/>
-    <hyperlink ref="I29" r:id="rId37" xr:uid="{129AB270-59C0-4501-B6EC-9626D7FC587B}"/>
-    <hyperlink ref="I33" r:id="rId38" xr:uid="{9621396B-EE77-4EC0-85EA-D9CF2492F76D}"/>
-    <hyperlink ref="I35" r:id="rId39" xr:uid="{7B46DDAA-2840-4B7C-806A-9D8C13D76907}"/>
-    <hyperlink ref="H31" r:id="rId40" xr:uid="{FAA28E75-E2F4-4BCF-9A90-108B43017BBB}"/>
+    <hyperlink ref="H20" r:id="rId14" xr:uid="{E454A7F1-60B0-46A2-BCAF-6EE451073594}"/>
+    <hyperlink ref="H21" r:id="rId15" xr:uid="{1127AC0B-364E-4EAD-9D99-A94EA5C42523}"/>
+    <hyperlink ref="H22" r:id="rId16" xr:uid="{898CFB37-C10F-4164-9DC8-B35726F71024}"/>
+    <hyperlink ref="H23" r:id="rId17" xr:uid="{9ECCB776-E8C3-4105-A6F7-2E6F2A184663}"/>
+    <hyperlink ref="H24" r:id="rId18" xr:uid="{4FC5ADBE-181E-43FF-9751-D6D427F0366F}"/>
+    <hyperlink ref="H25" r:id="rId19" xr:uid="{8A1E636A-763E-4FEA-AA46-C17108413427}"/>
+    <hyperlink ref="I25" r:id="rId20" xr:uid="{BC1D1921-7D71-457C-A023-855DF7FD4289}"/>
+    <hyperlink ref="H30" r:id="rId21" display="mailto:claudia.cubillos@slepaconcagua.gob.cl" xr:uid="{BF5D4A03-B565-4290-A323-81DEBCE5CFFB}"/>
+    <hyperlink ref="H32" r:id="rId22" display="mailto:claudio.wilson@sleplosalamos.gob.cl" xr:uid="{75417199-A8F7-4F2B-95A4-F7A17C2548B4}"/>
+    <hyperlink ref="H33" r:id="rId23" xr:uid="{54980B47-C332-416B-B63C-509B623066BB}"/>
+    <hyperlink ref="H34" r:id="rId24" xr:uid="{EA77E657-6305-4130-AE9B-9278175D24E4}"/>
+    <hyperlink ref="H35" r:id="rId25" display="mailto:araceli.nunez@sleptamarugal.gob.cl" xr:uid="{A213DA54-6A21-4C6A-BAD1-5943AE13A95A}"/>
+    <hyperlink ref="I36" r:id="rId26" xr:uid="{A0920DFD-228F-41BB-9846-5BA8CD1645DD}"/>
+    <hyperlink ref="H37" r:id="rId27" xr:uid="{47683FAC-4633-465C-A962-957D7E10B3B6}"/>
+    <hyperlink ref="I37" r:id="rId28" xr:uid="{8A354AB1-E770-4F79-B1BA-93ADD65AA4C2}"/>
+    <hyperlink ref="I31" r:id="rId29" xr:uid="{23A89A35-5FE5-4753-8C1C-C063A7CCAF17}"/>
+    <hyperlink ref="H36" r:id="rId30" xr:uid="{5E6E2E2A-9007-46B7-9964-2E09249D8F3A}"/>
+    <hyperlink ref="I34" r:id="rId31" xr:uid="{0011810F-DE97-45D0-9471-2DE01C3A5189}"/>
+    <hyperlink ref="I30" r:id="rId32" xr:uid="{A7A1E120-0ED5-475C-A8BB-BE81B51B7066}"/>
+    <hyperlink ref="I32" r:id="rId33" xr:uid="{301B3643-4756-45C1-BC55-FF9FD4821B41}"/>
+    <hyperlink ref="I29" r:id="rId34" xr:uid="{129AB270-59C0-4501-B6EC-9626D7FC587B}"/>
+    <hyperlink ref="I33" r:id="rId35" xr:uid="{9621396B-EE77-4EC0-85EA-D9CF2492F76D}"/>
+    <hyperlink ref="I35" r:id="rId36" xr:uid="{7B46DDAA-2840-4B7C-806A-9D8C13D76907}"/>
+    <hyperlink ref="H31" r:id="rId37" xr:uid="{FAA28E75-E2F4-4BCF-9A90-108B43017BBB}"/>
+    <hyperlink ref="I19" r:id="rId38" xr:uid="{AF7A88B2-1306-4BB1-A054-1302B134CD72}"/>
+    <hyperlink ref="H19" r:id="rId39" xr:uid="{3EF7D642-3A21-4881-BABE-BF8DDDA1FD2B}"/>
+    <hyperlink ref="H28" r:id="rId40" xr:uid="{B8BA04A9-AA68-44AD-B85E-C18D4164D1BB}"/>
+    <hyperlink ref="I28" r:id="rId41" display="mailto:carolina.villagra@sleppetorca.gob.cl" xr:uid="{B14E78B4-738B-461C-9C99-CD353D862E2D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId41"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId42"/>
   <tableParts count="1">
-    <tablePart r:id="rId42"/>
+    <tablePart r:id="rId43"/>
   </tableParts>
 </worksheet>
 </file>
@@ -3041,107 +3063,107 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
